--- a/output/pdf_financials_xlsx/QQ.xlsx
+++ b/output/pdf_financials_xlsx/QQ.xlsx
@@ -474,20 +474,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>7.409508</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>6.981391</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>6.841921</v>
       </c>
     </row>
     <row r="5">
@@ -496,20 +490,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -518,20 +506,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>7.409508</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6.981391</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>6.841921</v>
       </c>
     </row>
     <row r="7">
@@ -540,20 +522,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.495141</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.421227</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.325904</v>
       </c>
     </row>
     <row r="8">
@@ -578,20 +554,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -600,20 +570,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>8.305845</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>7.90905</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>7.349927</v>
       </c>
     </row>
     <row r="11">
@@ -622,20 +586,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.8963370000000001</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.927659</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.508006</v>
       </c>
     </row>
     <row r="12">
@@ -644,20 +602,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -666,20 +618,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,20 +634,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -710,20 +650,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.031779</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.147174</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.21384</v>
       </c>
     </row>
     <row r="16">
@@ -732,20 +666,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.824115</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.70987</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="17">
@@ -754,20 +682,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -820,20 +742,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.824115</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.70987</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="21">
@@ -842,20 +758,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -864,20 +774,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -886,20 +790,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.824115</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.70987</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="24">
@@ -924,20 +822,14 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -946,10 +838,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>41.20575</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -968,20 +858,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.824115</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.70987</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="28">
@@ -990,20 +874,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.516568</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.444867</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.450176</v>
       </c>
     </row>
     <row r="29">
@@ -1012,20 +890,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.307547</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.265003</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.162111</v>
       </c>
     </row>
     <row r="30">
@@ -1034,20 +906,14 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-4.150707442383489</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-3.795848133989344</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2.369378424568187</v>
       </c>
     </row>
     <row r="31">
@@ -1056,20 +922,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1078,20 +938,14 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-11.12239841025882</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-10.16803098408326</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-4.21029415569107</v>
       </c>
     </row>
     <row r="33">
@@ -1123,20 +977,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1145,20 +993,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.196362</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.050056</v>
       </c>
     </row>
     <row r="37">
@@ -1183,20 +1025,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1205,20 +1041,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1227,20 +1057,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1249,20 +1073,14 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.000181</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.045084</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.056668</v>
       </c>
     </row>
     <row r="42">
@@ -1271,20 +1089,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1293,20 +1105,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1315,20 +1121,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1337,20 +1137,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1359,20 +1153,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1397,20 +1185,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.021582</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.277664</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.775456</v>
       </c>
     </row>
     <row r="49">
@@ -1435,20 +1217,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1457,20 +1233,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1479,20 +1249,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1501,20 +1265,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1523,20 +1281,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1567,20 +1319,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1589,20 +1335,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1611,10 +1351,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>1.442529</v>
@@ -1629,20 +1367,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1651,20 +1383,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1673,20 +1399,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.146034</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.09296</v>
       </c>
     </row>
     <row r="62">
@@ -1700,15 +1420,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>1.588563</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1.100407</v>
       </c>
     </row>
     <row r="63">
@@ -1735,20 +1451,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1757,20 +1467,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1779,20 +1483,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.008527</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.204137</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.7486660000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1801,20 +1499,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1839,20 +1531,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1861,20 +1547,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1883,20 +1563,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1921,20 +1595,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1943,20 +1611,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0.004219</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.038605</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.029942</v>
       </c>
     </row>
     <row r="75">
@@ -1965,20 +1627,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1.193387</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2.019906</v>
       </c>
     </row>
     <row r="76">
@@ -2005,20 +1661,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2027,20 +1677,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2049,20 +1693,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2076,10 +1714,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>-2.052386372785988e-05</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -2093,20 +1729,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2115,20 +1745,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2137,20 +1761,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2159,20 +1777,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2181,20 +1793,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>1.154606</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0.327701</v>
       </c>
     </row>
     <row r="86">
@@ -2208,15 +1814,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C86" s="3" t="n">
+        <v>1.154606</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.327701</v>
       </c>
     </row>
     <row r="87">
@@ -2243,20 +1845,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>6.171042</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>26.651042</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>26.801042</v>
       </c>
     </row>
     <row r="89">
@@ -2265,20 +1861,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2303,20 +1893,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2325,20 +1909,14 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2347,20 +1925,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2374,15 +1946,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>-0.633409</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>-0.671474</v>
       </c>
     </row>
     <row r="95">
@@ -2391,20 +1959,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2418,15 +1980,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>-0.633409</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.671474</v>
       </c>
     </row>
     <row r="97">
@@ -2440,15 +1998,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C97" s="3" t="n">
+        <v>-0.269691247506541</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-0.3051958942631404</v>
       </c>
     </row>
     <row r="98">
@@ -2464,20 +2018,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.824115</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.70987</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="100">
@@ -2486,20 +2034,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2524,20 +2066,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>-0.08285099999999999</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0.111559</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0.023418</v>
       </c>
     </row>
     <row r="103">
@@ -2546,20 +2082,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.009887999999999999</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.000797</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.008041</v>
       </c>
     </row>
     <row r="104">
@@ -2568,10 +2098,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.293644</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.12421</v>
@@ -2586,20 +2114,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>-0.015144</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0.024386</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>-0.008663000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -2608,20 +2130,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.373987</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.256049</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.106143</v>
       </c>
     </row>
     <row r="107">
@@ -2630,20 +2146,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2652,20 +2162,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2674,20 +2178,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2696,20 +2194,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2734,20 +2226,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2756,20 +2242,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2778,20 +2258,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2800,20 +2274,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2822,20 +2290,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2844,20 +2306,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2866,20 +2322,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2904,20 +2354,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2926,20 +2370,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2948,20 +2386,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2970,20 +2402,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2992,20 +2418,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3014,20 +2434,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3036,20 +2450,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3080,20 +2488,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3140,20 +2542,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3162,10 +2558,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.258258</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.175562</v>
@@ -3202,20 +2596,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.152104</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-0.027216</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-0.004672</v>
       </c>
     </row>
     <row r="135">
@@ -3224,20 +2612,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.08764</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.207667</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0.177763</v>
       </c>
     </row>
   </sheetData>
@@ -3379,7 +2761,11 @@
           <t>Due from related parties (Note 13)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -3759,7 +3145,11 @@
           <t>Due to related parties (Note 13)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4443,7 +3833,11 @@
           <t>Due to related parties (Note 13) -</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.008527</v>
       </c>
@@ -4530,7 +3924,11 @@
           <t>Loan payable (Note 17) -</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.005</v>
       </c>
@@ -4559,7 +3957,11 @@
           <t>Government loan payable (Note 17) -</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
@@ -4741,7 +4143,11 @@
           <t>Net loss</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.824115</v>
       </c>
@@ -5062,7 +4468,11 @@
           <t>Prepaid expenses and deposits</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.009887999999999999</v>
       </c>
@@ -5116,7 +4526,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>-0.08285099999999999</v>
       </c>
@@ -5203,7 +4617,11 @@
           <t>Deferred revenue</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>-0.015144</v>
       </c>
@@ -5713,7 +5131,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>42,906,845 26,171,042 3,320,463</t>
+          <t>Shares Amount Reserves Received Deficit Total</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5836,7 +5254,11 @@
           <t>Comprehensive loss for the year - - - -</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-0.824115</v>
       </c>
@@ -5923,7 +5345,11 @@
           <t>Comprehensive loss for the year - - - -</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -6043,7 +5469,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>-0.293644</v>
       </c>
@@ -6188,7 +5618,11 @@
           <t>DECREASE IN CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>-0.258258</v>
       </c>
@@ -6515,7 +5949,11 @@
           <t>REVENUE total</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -6685,7 +6123,11 @@
           <t>Management fees (Note 13)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>0.256519</v>
       </c>
@@ -6712,7 +6154,11 @@
           <t>Office and miscellaneous (Note 13)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.21722</v>
       </c>
@@ -6766,7 +6212,11 @@
           <t>Regulatory fees</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>0.021402</v>
       </c>
@@ -6959,7 +6409,11 @@
           <t>EXPENSES total</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>8.305845</v>
       </c>
@@ -6986,7 +6440,11 @@
           <t>LOSS BEFORE OTHER ITEMS</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>-0.8963370000000001</v>
       </c>
@@ -7135,7 +6593,11 @@
           <t>Other income (Note 13)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -7164,7 +6626,11 @@
           <t>NET LOSS AND COMPREHENSIVE LOSS</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -7313,7 +6779,11 @@
           <t>REVENUES total</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>7.409508</v>
       </c>
@@ -7468,7 +6938,11 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E141" s="5" t="n">
         <v>0.031779</v>
       </c>
@@ -7497,7 +6971,11 @@
           <t>NET LOSS AND COMPREHENSIVE LOSS (</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
         <v>-0.824115</v>
       </c>

--- a/output/pdf_financials_xlsx/QQ.xlsx
+++ b/output/pdf_financials_xlsx/QQ.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/QQ.xlsx
+++ b/output/pdf_financials_xlsx/QQ.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.0008</v>
+        <v>0.0208</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.196362</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0008</v>
+        <v>0.0208</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.196362</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.000181</v>
+        <v>0.040181</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0.045084</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.000181</v>
+        <v>0.040181</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.045084</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0.052531</v>
+        <v>0.352531</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0.240972</v>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.021582</v>
+        <v>0.061582</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.277664</v>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0.07509399999999999</v>
+        <v>0.475094</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.760082</v>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>1.829944</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>1.442529</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0</v>
+        <v>0.193756</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0.146034</v>
@@ -1421,10 +1421,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>2.0237</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>1.588563</v>
@@ -1439,10 +1437,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>2.498794</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>2.348645</v>
@@ -1490,7 +1486,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0.008527</v>
+        <v>0.028527</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0.204137</v>
@@ -1522,7 +1518,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.071233</v>
+        <v>0.471233</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.5954429999999999</v>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>0.005</v>
+        <v>0.135</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1.3e-05</v>
+        <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>0</v>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.005</v>
+        <v>0.135</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.3e-05</v>
+        <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -1586,7 +1582,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>0.004219</v>
+        <v>0.014219</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0.038605</v>
@@ -1618,7 +1614,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>0.004219</v>
+        <v>0.014219</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0.038605</v>
@@ -1634,10 +1630,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0</v>
+        <v>0.719189</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.193387</v>
+        <v>1.1934</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>2.019906</v>
@@ -1649,10 +1645,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>1.339641</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>1.827448</v>
@@ -1715,13 +1709,13 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>-2.052386372785988e-05</v>
+      <c r="B80" s="3" t="n">
+        <v>-0.3345401559700549</v>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -1800,7 +1794,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0</v>
+        <v>1.562692</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>1.154606</v>
@@ -1815,10 +1809,8 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>1.562692</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>1.154606</v>
@@ -1833,10 +1825,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>2.902333</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>2.982054</v>
@@ -1852,7 +1842,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>6.171042</v>
+        <v>26.171042</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>26.651042</v>
@@ -1947,10 +1937,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>-0.403539</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>-0.633409</v>
@@ -1981,10 +1969,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>-0.403539</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>-0.633409</v>
@@ -1999,10 +1985,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>-0.1614935044665547</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>-0.269691247506541</v>
@@ -2639,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2706,10 +2690,8 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0.196362</v>
@@ -2739,10 +2721,8 @@
           <t>AccountsReceivable</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E3" s="5" t="n">
+        <v>0.040181</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.045084</v>
@@ -2801,10 +2781,8 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="5" t="n">
+        <v>0.019365</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.032107</v>
@@ -2836,10 +2814,8 @@
           <t>PrepaidAssets</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.042217</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.04142</v>
@@ -2869,10 +2845,8 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>0.352531</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.240972</v>
@@ -2902,10 +2876,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="5" t="n">
+        <v>0.475094</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.760082</v>
@@ -2931,10 +2903,8 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="5" t="n">
+        <v>0.035</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0.035</v>
@@ -2960,10 +2930,8 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="5" t="n">
+        <v>0.158756</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.111034</v>
@@ -2993,10 +2961,8 @@
           <t>NetPPE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="5" t="n">
+        <v>1.829944</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>1.442529</v>
@@ -3026,10 +2992,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="5" t="n">
+        <v>2.498794</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>2.348645</v>
@@ -3059,10 +3023,8 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="5" t="n">
+        <v>0.471233</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.5954429999999999</v>
@@ -3123,10 +3085,8 @@
           <t>CurrentDeferredRevenue</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="5" t="n">
+        <v>0.014219</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0.038605</v>
@@ -3156,10 +3116,8 @@
           <t>OtherPayable</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="5" t="n">
+        <v>0.028527</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3187,10 +3145,8 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>0.169006</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0.737947</v>
@@ -3216,10 +3172,8 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E18" s="5" t="n">
+        <v>0.432363</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0.455453</v>
@@ -3249,10 +3203,8 @@
           <t>CurrentLiabilities</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E19" s="5" t="n">
+        <v>1.339641</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>1.827448</v>
@@ -3278,10 +3230,8 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="5" t="n">
+        <v>1.562692</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1.154606</v>
@@ -3311,10 +3261,8 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="5" t="n">
+        <v>2.902333</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>2.982054</v>
@@ -3344,10 +3292,8 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>26.171042</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>26.651042</v>
@@ -3373,10 +3319,8 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="5" t="n">
+        <v>3.320463</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>3.320463</v>
@@ -3406,10 +3350,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>-29.895044</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>-30.604914</v>
@@ -3435,10 +3377,8 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>-0.403539</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>-0.633409</v>
@@ -3464,10 +3404,8 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="5" t="n">
+        <v>2.498794</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>2.348645</v>
@@ -3518,19 +3456,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 196,362</t>
+          <t>Loan payable (Note 17)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.075</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3551,19 +3491,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts receivable 45,084</t>
+          <t>Government loan payable (Note 17)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AccountsReceivable</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.000181</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.06</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3584,15 +3526,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sales taxes recoverable 32,107</t>
+          <t>Deposit received (Note 10)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>0.009365</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.089293</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3608,24 +3552,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Contingencies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prepaid expenses 41,420</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
+          <t>APPROVED ON BEHALF OF THE BOARD ON OCTOBER</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>0.002217</v>
+        <v>0.002024</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>4e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3636,91 +3576,87 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inventory (Note 5) 240,972</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.052531</v>
+        <v>-0.824115</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.70987</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Total current assets 760,082</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.07509399999999999</v>
+        <v>0.516568</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.444867</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.450176</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Security deposit 35,000</t>
+          <t>Gain from termination of leases</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.004001</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3e-06</v>
+        <v>-0.004764</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3731,25 +3667,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Investment in sublease (Note 20) 111,034</t>
+          <t>Investment in sublease</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>0.058756</v>
+        <v>-0.158756</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1e-06</v>
+        <v>-0.001399</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3760,29 +3696,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 595,443</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0.071233</v>
+          <t>Gain on termination of Vernon store</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4e-06</v>
+        <v>-0.036191</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3793,29 +3727,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deferred revenue 38,605</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CurrentDeferredRevenue</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.004219</v>
+          <t>Loan forgiveness (Note 17)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>1e-06</v>
+        <v>-0.02</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3826,311 +3758,293 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Due to related parties (Note 13) -</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>OtherPayable</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.008527</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accrued interest and foreign exchange on loans payable due to related parties</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.079036</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Loans payable to related parties (Note 13) 737,947</t>
+          <t>Interest income on sublease</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>0.069006</v>
+        <v>-0.000647</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00966</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.006091</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lease liabilities – (Note 19) 455,453</t>
+          <t>Lease interest expense</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.032363</v>
+        <v>0.151358</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.145923</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.114204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Loan payable (Note 17) -</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
+          <t>Add back non-cash items total</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.355087</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.191094</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.34926</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Government loan payable (Note 17) -</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CurrentDebt</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>0.007764</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004903</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.011584</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Deposit received (Note 10) -</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
-        <v>0.009292999999999999</v>
+        <v>0.009887999999999999</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>8e-06</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000797</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.008041</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DEFICIENCY</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Share capital (Note 7) 26,651,042</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
+          <t>Sales taxes recoverable</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>6.171042</v>
+        <v>-0.017811</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.012742</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.06662</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Reserves 3,320,463 3 ,320,463</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>ChangeInInventory</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-29.895044</v>
+        <v>-0.08285099999999999</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-30.604914</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.111559</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.023418</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reserves 3,320,463 3 ,320,463</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Total deficiency</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>-0.403539</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.633409</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.12421</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.101273</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Contingencies</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>APPROVED ON BEHALF OF THE BOARD ON OCTOBER</t>
+          <t>Due to (due from) related parties</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0.002024</v>
+        <v>-0.188651</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.232664</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.127302</v>
       </c>
     </row>
     <row r="48">
@@ -4141,27 +4055,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Deferred revenue</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-0.824115</v>
+        <v>-0.015144</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.70987</v>
+        <v>0.024386</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.288065</v>
+        <v>-0.008663000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4172,27 +4086,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>CASH PROVIDED BY (USED IN ) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.516568</v>
+        <v>-0.935536</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.444867</v>
+        <v>-0.180451</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.450176</v>
+        <v>0.182435</v>
       </c>
     </row>
     <row r="50">
@@ -4203,25 +4117,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gain from termination of leases</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Issuance of common shares, net</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>-0.004001</v>
+        <v>0.6448</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.004764</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.402303</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="51">
@@ -4232,20 +4148,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Investment in sublease</t>
+          <t>Shares issued on conversion of debt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>-0.158756</v>
+        <v>0.135</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.001399</v>
+        <v>0.002697</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4261,12 +4177,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gain on termination of Vernon store</t>
+          <t>Loan repayments</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4276,7 +4192,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.036191</v>
+        <v>-0.04</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4292,12 +4208,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Loan forgiveness (Note 17)</t>
+          <t>Loan repayments to related parties</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4306,13 +4222,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.228305</v>
       </c>
     </row>
     <row r="54">
@@ -4323,12 +4239,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accrued interest and foreign exchange on loans payable due to related parties</t>
+          <t>Proceeds from loans payable to related parties</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4337,13 +4253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" s="5" t="n">
+        <v>0.568941</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.079036</v>
+        <v>0.289051</v>
       </c>
     </row>
     <row r="55">
@@ -4354,23 +4268,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Interest income on sublease</t>
+          <t>Lease payments</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>-0.000647</v>
+        <v>-0.5578</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.00966</v>
+        <v>-0.49761</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.006091</v>
+        <v>-0.509815</v>
       </c>
     </row>
     <row r="56">
@@ -4381,23 +4295,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lease interest expense</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>CASH PROVIDED BY (USED IN ) FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>0.151358</v>
+        <v>0.435881</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.145923</v>
+        <v>0.436331</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.114204</v>
+        <v>-0.324069</v>
       </c>
     </row>
     <row r="57">
@@ -4408,23 +4326,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Add back non-cash items total</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Disposal (purchase) of property and equipment</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
-        <v>-0.355087</v>
+        <v>0.152104</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-0.191094</v>
+        <v>-0.027216</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.34926</v>
+        <v>-0.004672</v>
       </c>
     </row>
     <row r="58">
@@ -4435,27 +4357,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Deposits received (refunded)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.007764</v>
+        <v>0.089293</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.004903</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.011584</v>
+        <v>-0.053102</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4466,27 +4386,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>CASH PROVIDED BY (USED IN ) INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.009887999999999999</v>
+        <v>0.241397</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.000797</v>
+        <v>-0.080318</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.008041</v>
+        <v>-0.004672</v>
       </c>
     </row>
     <row r="60">
@@ -4497,23 +4417,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sales taxes recoverable</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>-0.017811</v>
+          <t>CHANGE IN CASH AND CASH EQUIVALENTS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.012742</v>
+        <v>0.175562</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.06662</v>
+        <v>-0.146306</v>
       </c>
     </row>
     <row r="61">
@@ -4524,27 +4450,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ChangeInInventory</t>
-        </is>
-      </c>
+          <t>CASH AND CASH EQUIVALENTS – BEGINNING</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>-0.08285099999999999</v>
+        <v>0.279058</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.111559</v>
+        <v>0.0208</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.023418</v>
+        <v>0.196362</v>
       </c>
     </row>
     <row r="62">
@@ -4555,29 +4477,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH AND CASH EQUIVALENTS – ENDING</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.12421</v>
+        <v>0.196362</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.101273</v>
+        <v>0.050056</v>
       </c>
     </row>
     <row r="63">
@@ -4588,23 +4504,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Due to (due from) related parties</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>-0.188651</v>
+          <t>Issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-0.232664</v>
+        <v>-0.185301</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.127302</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="64">
@@ -4615,27 +4537,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>-0.015144</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.024386</v>
+          <t>Loans payable to related parties</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.008663000000000001</v>
+        <v>-0.456882</v>
       </c>
     </row>
     <row r="65">
@@ -4646,27 +4568,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CASH PROVIDED BY (USED IN ) OPERATING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>-0.935536</v>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-0.180451</v>
+        <v>-0.403539</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.182435</v>
+        <v>-29.895044</v>
       </c>
     </row>
     <row r="66">
@@ -4677,29 +4597,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Issuance of common shares, net</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>As at May 31,</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>0.402303</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.125</v>
+        <v>0.002023</v>
       </c>
     </row>
     <row r="67">
@@ -4710,12 +4628,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of debt</t>
+          <t>Private placement of units 13,410,100 402,303 - -</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -4725,7 +4643,7 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.002697</v>
+        <v>0.402303</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4741,12 +4659,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Loan repayments</t>
+          <t>Shares issued on debt conversion 2,589,900 77,697 - -</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -4756,7 +4674,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.077697</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4772,27 +4690,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Loan repayments to related parties</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Comprehensive loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="5" t="n">
+        <v>-0.70987</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.228305</v>
+        <v>-0.70987</v>
       </c>
     </row>
     <row r="70">
@@ -4803,12 +4723,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Shares          Amount       Reserves         Received               Deficit         Total</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Proceeds from loans payable to related parties</t>
+          <t>As at May 31, 2024 58,906,845 26,651,042 3,320,463</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -4818,10 +4738,10 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.568941</v>
+        <v>-0.633409</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.289051</v>
+        <v>-30.604914</v>
       </c>
     </row>
     <row r="71">
@@ -4832,23 +4752,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lease payments</t>
+          <t>Private placement of units 5,000,000 150,000 100,000 -</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>-0.5578</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.49761</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>-0.509815</v>
+        <v>0.25</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4859,27 +4783,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CASH PROVIDED BY (USED IN ) FINANCING ACTIVITIES</t>
+          <t>Comprehensive loss for the year - - - -</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0.435881</v>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.436331</v>
+        <v>-0.288065</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.324069</v>
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="73">
@@ -4890,27 +4816,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Disposal (purchase) of property and equipment</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0.152104</v>
+          <t>As at May 31, 2025 63,906,845 26,801,042 3,420,463 -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.027216</v>
+        <v>-0.671474</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.004672</v>
+        <v>-30.892979</v>
       </c>
     </row>
     <row r="74">
@@ -4921,20 +4845,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Deposits received (refunded)</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>0.089293</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.053102</v>
+        <v>-0.021583</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4950,27 +4876,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Add back non-cash items</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CASH PROVIDED BY (USED IN ) INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Gain on sublease</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0.241397</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-0.080318</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-0.004672</v>
+        <v>-0.013911</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4981,29 +4907,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHANGE IN CASH AND CASH EQUIVALENTS</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-0.293644</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.175562</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>-0.146306</v>
+        <v>0.12421</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5014,23 +4940,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS – BEGINNING</t>
+          <t>Loans received (repayments)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>0.279058</v>
+        <v>0.044875</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.196362</v>
+        <v>-0.04</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5041,23 +4969,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS – ENDING</t>
+          <t>Loans payable to related parties</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.169006</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.196362</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.050056</v>
+        <v>0.568941</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5068,29 +4998,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Issuance of common shares</t>
+          <t>DECREASE IN CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>-0.258258</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.185301</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>-0.125</v>
+        <v>0.175562</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -5101,27 +5031,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Loans payable to related parties</t>
+          <t>As at May 31, 2022 25,277,678 25,313,167 3,278,463 150,200</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>-0.456882</v>
+      <c r="E80" s="5" t="n">
+        <v>-0.329099</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-29.070929</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5132,25 +5060,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Private placement of units 15,100,000 753,000 42,000 (150,200)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>-0.403539</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>-29.895044</v>
+      <c r="E81" s="5" t="n">
+        <v>0.6448</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -5161,27 +5091,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>As at May 31,</t>
+          <t>Shares issued on debt conversion 1,200,000 60,000 - -</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G82" s="5" t="n">
-        <v>0.002023</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5192,20 +5122,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Private placement of units 13,410,100 402,303 - -</t>
+          <t>Shares issued on debt settlement 1,329,167 44,875 - -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
-        <v>0.402303</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.402303</v>
+        <v>0.044875</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5221,22 +5153,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Shares issued on debt conversion 2,589,900 77,697 - -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.824115</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.077697</v>
+        <v>-0.824115</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5252,27 +5186,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>As at May 31, 2023 42,906,845 26,171,042 3,320,463 -</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>-0.824115</v>
+        <v>-0.403539</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-0.70987</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>-0.70987</v>
+        <v>-29.895044</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5283,25 +5215,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>As at May 31, 2024 58,906,845 26,651,042 3,320,463</t>
+          <t>Private placement of units 13,410,100 402,303 - -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.633409</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>-30.604914</v>
+      <c r="E86" s="5" t="n">
+        <v>0.402303</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5312,22 +5246,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Private placement of units 5,000,000 150,000 100,000 -</t>
+          <t>Shares issued for debt conversion 2,589,900 77,697 - -</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0.25</v>
+      <c r="E87" s="5" t="n">
+        <v>0.077697</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5343,45 +5277,41 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Shares          Amount    Reserves          Received          Deficit            Total</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>As at May 31, 2024 58,906,845 26,651,042 3,320,463 -</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>-0.633409</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.288065</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>-0.288065</v>
+        <v>-30.604914</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>As at May 31, 2025 63,906,845 26,801,042 3,420,463 -</t>
+          <t>Retail sales</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5391,494 +5321,472 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.671474</v>
+        <v>6.687813</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-30.892979</v>
+        <v>6.562962</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
+          <t>Training services</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>-0.021583</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.293578</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.278959</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Add back non-cash items</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gain on sublease</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>-0.013911</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>REVENUE total</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>6.981391</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>6.841921</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Accounting and legal (Note 13)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
-        <v>-0.293644</v>
+        <v>0.183607</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.12421</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.207273</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.134698</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Issuance of common shares, ne(cid:32)t</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
-        <v>0.6448</v>
+        <v>0.0338</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.402303</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.029622</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.032632</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of debt(cid:32)</t>
+          <t>Bank charges and finance fees</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" s="5" t="n">
-        <v>0.135</v>
+        <v>0.289206</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.002697</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.317068</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.31937</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Loans received (repayments)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0.044875</v>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.444867</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.450176</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Loans payable to related parties(cid:32)</t>
+          <t>Investor and finance development (Note 13)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
-        <v>0.169006</v>
+        <v>0.178826</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.568941</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.086351</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.024784</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DECREASE IN CASH AND CASH EQUIVALENTS</t>
+          <t>Management fees (Note 13)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>-0.258258</v>
+        <v>0.256519</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.175562</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.212822</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.161841</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>As at May 31, 2022 25,277,678 25,313,167 3 ,278,463 150,200</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Office and miscellaneous (Note 13)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
-        <v>-0.329099</v>
+        <v>0.21722</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-29.070929</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.189736</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.139198</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Private placement of units 15,100,000 753,000 42,000 (150,200)</t>
+          <t>On-Track TV development costs (Note 11 and 12)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" s="5" t="n">
-        <v>0.6448</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.12714</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.017333</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.065925</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Shares issued on debt conversion 1,200,000 60,000 - -</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021402</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.018669</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.024865</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Shares issued on debt settlement 1,329,167 44,875 - -</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Research and development (Note 13)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
-        <v>0.044875</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.25632</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.334065</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.220544</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>As at May 31, 2023 42,906,845 26,171,042 3,320,463 -</t>
+          <t>Retail inventory (Note 5)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" s="5" t="n">
-        <v>-0.403539</v>
+        <v>4.478266</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-29.895044</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.393828</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>4.336536</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>As at May 31, 2023 42,906,845 26,171,042 3 ,320,463 -</t>
+          <t>Subcontractors (Note 13)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="n">
-        <v>-0.403539</v>
+        <v>0.287747</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-29.895044</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.151522</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.146441</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Shares issued for debt conversion 2,589,900 77,697 - -</t>
+          <t>Telephone and internet</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" s="5" t="n">
-        <v>0.077697</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.029655</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.027168</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.032762</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shares Amount Reserves Received Deficit Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>As at May 31, 2024 58,906,845 26,651,042 3,320,463 -</t>
+          <t>Travel and business development (Note 13)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" s="5" t="n">
-        <v>-0.633409</v>
+        <v>0.578576</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-30.604914</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.648806</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.424421</v>
       </c>
     </row>
     <row r="106">
@@ -5889,25 +5797,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Retail sales</t>
+          <t>Wages and benefits (Note 13)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="5" t="n">
+        <v>0.830676</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>6.687813</v>
+        <v>0.82992</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>6.562962</v>
+        <v>0.835734</v>
       </c>
     </row>
     <row r="107">
@@ -5918,25 +5824,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Training services</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>8.305845</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.293578</v>
+        <v>7.90905</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.278959</v>
+        <v>7.349927</v>
       </c>
     </row>
     <row r="108">
@@ -5947,29 +5855,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>REVENUE total</t>
+          <t>LOSS BEFORE OTHER ITEMS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-0.8963370000000001</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>6.981391</v>
+        <v>-0.927659</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>6.841921</v>
+        <v>-0.508006</v>
       </c>
     </row>
     <row r="109">
@@ -5980,23 +5886,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Accounting and legal (Note 13)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
-        <v>0.183607</v>
+        <v>0.0009479999999999999</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.207273</v>
+        <v>0.00966</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.134698</v>
+        <v>0.006101</v>
       </c>
     </row>
     <row r="110">
@@ -6007,23 +5917,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Gain on termination of leases</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" s="5" t="n">
-        <v>0.0338</v>
+        <v>0.004001</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.029622</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.032632</v>
+        <v>0.004764</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -6034,23 +5946,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bank charges and finance fees</t>
+          <t>Gain on termination of Vernon store</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>0.289206</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.317068</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0.31937</v>
+        <v>0.036191</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6061,29 +5977,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Loan forgiveness (Note 17)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.444867</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.450176</v>
+        <v>0.02</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6094,23 +6008,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Investor and finance development (Note 13)</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>0.178826</v>
+          <t>Other income (Note 13)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.086351</v>
+        <v>0.147174</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.024784</v>
+        <v>0.21384</v>
       </c>
     </row>
     <row r="114">
@@ -6121,27 +6041,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Management fees (Note 13)</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.256519</v>
+        <v>-0.824115</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.212822</v>
+        <v>-0.70987</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.161841</v>
+        <v>-0.288065</v>
       </c>
     </row>
     <row r="115">
@@ -6152,27 +6072,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Office and miscellaneous (Note 13)</t>
+          <t>LOSS PER SHARE BASIC AND DILUTED</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0.21722</v>
+        <v>-2e-08</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.189736</v>
+        <v>-1e-08</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.139198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6183,23 +6103,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>On-Track TV development costs (Note 11 and 12)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
-        <v>0.12714</v>
+        <v>35.785258</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.017333</v>
+        <v>47.939632</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.065925</v>
+        <v>59.126023</v>
       </c>
     </row>
     <row r="117">
@@ -6210,27 +6134,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Retail sales</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" s="5" t="n">
-        <v>0.021402</v>
+        <v>6.865897</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.018669</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>0.024865</v>
+        <v>6.687813</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6241,27 +6163,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Research and development (Note 13)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Training services and software sales</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" s="5" t="n">
-        <v>0.25632</v>
+        <v>0.543611</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.334065</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.220544</v>
+        <v>0.293578</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6272,23 +6192,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Retail inventory (Note 5)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>REVENUES total</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
-        <v>4.478266</v>
+        <v>7.409508</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>4.393828</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>4.336536</v>
+        <v>6.981391</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6304,18 +6230,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Subcontractors (Note 13)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
-        <v>0.287747</v>
+        <v>0.516568</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.151522</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.146441</v>
+        <v>0.444867</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -6331,18 +6263,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telephone and internet</t>
+          <t>Software development costs (Note 12)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" s="5" t="n">
-        <v>0.029655</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>0.027168</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>0.032762</v>
+        <v>0.020317</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -6353,23 +6289,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Travel and business development (Note 13)</t>
+          <t>Gain on sublease (Note 20)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" s="5" t="n">
-        <v>0.578576</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.648806</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.424421</v>
+        <v>0.013911</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -6380,23 +6320,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 13)</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" s="5" t="n">
-        <v>0.830676</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.82992</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>0.835734</v>
+        <v>0.021583</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -6407,588 +6351,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>8.305845</v>
+        <v>0.031779</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>7.90905</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>7.349927</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>LOSS BEFORE OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>-0.8963370000000001</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>-0.927659</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>-0.508006</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>0.0009479999999999999</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>0.00966</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.006101</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Gain on termination of leases</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>0.004001</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0.004764</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Gain on termination of Vernon store</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>0.036191</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Loan forgiveness (Note 17)</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Other income (Note 13)</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="n">
         <v>0.147174</v>
       </c>
-      <c r="G130" s="5" t="n">
-        <v>0.21384</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>-0.70987</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>-0.288065</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>LOSS PER SHARE BASIC AND DILUTED</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>35.785258</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>47.939632</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>59.126023</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>REVENUES</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Retail sales</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" s="5" t="n">
-        <v>6.865897</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>6.687813</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>REVENUES</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Training services and software sales</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>0.543611</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>0.293578</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>REVENUES</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>REVENUES total</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>7.409508</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>6.981391</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="n">
-        <v>0.516568</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>0.444867</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Software development costs (Note 12)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>0.020317</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Gain on sublease (Note 20)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>0.013911</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Gain on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>0.021583</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>0.031779</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>0.147174</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS (</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="n">
-        <v>-0.824115</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.70987</v>
-      </c>
-      <c r="G142" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/QQ.xlsx
+++ b/output/pdf_financials_xlsx/QQ.xlsx
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.320463</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.320463</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.420463</v>
       </c>
     </row>
     <row r="93">
@@ -3318,7 +3318,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>3.320463</v>
       </c>

--- a/output/pdf_financials_xlsx/QQ.xlsx
+++ b/output/pdf_financials_xlsx/QQ.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009479999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00966</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006101</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.824115</v>
+        <v>-0.825063</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.70987</v>
+        <v>-0.71953</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.288065</v>
+        <v>-0.294166</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.307547</v>
+        <v>-0.308495</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.265003</v>
+        <v>-0.274663</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.162111</v>
+        <v>0.15601</v>
       </c>
     </row>
     <row r="30">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4.150707442383489</v>
+        <v>-4.163501814155541</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3.795848133989344</v>
+        <v>-3.934215975011283</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.369378424568187</v>
+        <v>2.280207561589793</v>
       </c>
     </row>
     <row r="31">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.5578</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.49761</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.509815</v>
       </c>
     </row>
     <row r="125">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.5578</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.49761</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.509815</v>
       </c>
     </row>
     <row r="126">
@@ -4280,7 +4280,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-0.5578</v>
       </c>
@@ -5900,7 +5904,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
